--- a/docs/demo-data/GNDEC/Timetabl_blank_template.xlsx
+++ b/docs/demo-data/GNDEC/Timetabl_blank_template.xlsx
@@ -597,7 +597,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Shared halls (lecture theatres, seminar hall, drawing halls, workshops) are added by the College Admin in Setup.</t>
+          <t xml:space="preserve">  Rooms every department may use (e.g. a seminar hall) are added by the College Admin in Setup as shared rooms.</t>
         </is>
       </c>
     </row>
